--- a/templates/CAPITANIA YIELD 120 - template.xlsx
+++ b/templates/CAPITANIA YIELD 120 - template.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="20370" yWindow="-60" windowWidth="20730" windowHeight="11040" tabRatio="711" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="20355" yWindow="-11640" windowWidth="20730" windowHeight="11040" tabRatio="711" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Email" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Email" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="DataAnálise">Email!$A$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Email'!$B$6:$H$44</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Email'!$B$6:$H$45</definedName>
   </definedNames>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -772,18 +772,18 @@
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="166" fontId="31" fillId="38" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="32" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="47">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="36" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="justify" vertical="justify" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="32" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="47">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="36" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="51">
@@ -1202,7 +1202,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J48"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
     <col width="13.42578125" customWidth="1" style="47" min="1" max="1"/>
@@ -1210,8 +1210,8 @@
     <col width="5.42578125" customWidth="1" style="47" min="9" max="9"/>
     <col width="23.140625" bestFit="1" customWidth="1" style="47" min="10" max="10"/>
     <col width="23.42578125" bestFit="1" customWidth="1" style="47" min="11" max="11"/>
-    <col width="9.140625" customWidth="1" style="47" min="12" max="19"/>
-    <col width="9.140625" customWidth="1" style="47" min="20" max="16384"/>
+    <col width="9.140625" customWidth="1" style="47" min="12" max="20"/>
+    <col width="9.140625" customWidth="1" style="47" min="21" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1360,14 +1360,14 @@
     <row r="20" ht="15.95" customFormat="1" customHeight="1" s="26">
       <c r="B20" s="27" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C20" s="28" t="n">
-        <v>1.50614996</v>
+        <v>1.51687153</v>
       </c>
       <c r="D20" s="29" t="n">
-        <v>0.0005487922084008723</v>
+        <v>0.0006529665167607224</v>
       </c>
       <c r="E20" s="29" t="n">
         <v>0.0005426623598601132</v>
@@ -1376,23 +1376,23 @@
         <v>0.0005821700069987834</v>
       </c>
       <c r="G20" s="30" t="n">
-        <v>1.011295879342616</v>
+        <v>1.20326480157762</v>
       </c>
       <c r="H20" s="30" t="n">
-        <v>0.9426665781530362</v>
+        <v>1.121607964874231</v>
       </c>
     </row>
     <row r="21" ht="15.95" customFormat="1" customHeight="1" s="26">
       <c r="B21" s="31" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C21" s="32" t="n">
-        <v>1.50532385</v>
+        <v>1.51588171</v>
       </c>
       <c r="D21" s="33" t="n">
-        <v>0.0006428528253972221</v>
+        <v>0.0006388415785367751</v>
       </c>
       <c r="E21" s="33" t="n">
         <v>0.0005426623598601132</v>
@@ -1401,23 +1401,23 @@
         <v>0.0005821700069987834</v>
       </c>
       <c r="G21" s="34" t="n">
-        <v>1.184627630268913</v>
+        <v>1.17723583906106</v>
       </c>
       <c r="H21" s="34" t="n">
-        <v>1.104235562926493</v>
+        <v>1.097345398864064</v>
       </c>
     </row>
     <row r="22" ht="15.95" customFormat="1" customHeight="1" s="26">
       <c r="B22" s="31" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C22" s="32" t="n">
-        <v>1.50435677</v>
+        <v>1.51491392</v>
       </c>
       <c r="D22" s="33" t="n">
-        <v>0.0006814794131873025</v>
+        <v>0.000571381839589602</v>
       </c>
       <c r="E22" s="33" t="n">
         <v>0.0005426623598601132</v>
@@ -1426,23 +1426,23 @@
         <v>0.0005821700069987834</v>
       </c>
       <c r="G22" s="34" t="n">
-        <v>1.255807411007783</v>
+        <v>1.052923294213536</v>
       </c>
       <c r="H22" s="34" t="n">
-        <v>1.170584889284285</v>
+        <v>0.9814690429264866</v>
       </c>
     </row>
     <row r="23" ht="15.95" customFormat="1" customHeight="1" s="26">
       <c r="B23" s="31" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C23" s="32" t="n">
-        <v>1.50333228</v>
+        <v>1.51404882</v>
       </c>
       <c r="D23" s="33" t="n">
-        <v>0.0006720393873311803</v>
+        <v>0.0006428493413423997</v>
       </c>
       <c r="E23" s="33" t="n">
         <v>0.0005426623598601132</v>
@@ -1451,35 +1451,35 @@
         <v>0.0005821700069987834</v>
       </c>
       <c r="G23" s="34" t="n">
-        <v>1.238411647906477</v>
+        <v>1.184621209969515</v>
       </c>
       <c r="H23" s="34" t="n">
-        <v>1.15436965019152</v>
+        <v>1.104229578326152</v>
       </c>
     </row>
     <row r="24" ht="15.95" customFormat="1" customHeight="1" s="26">
       <c r="B24" s="31" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C24" s="32" t="n">
-        <v>1.50232266</v>
+        <v>1.51307614</v>
       </c>
       <c r="D24" s="33" t="n">
-        <v>0.0006568147517835854</v>
+        <v>0.000659436436066585</v>
       </c>
       <c r="E24" s="33" t="n">
-        <v>0.0005513106415402369</v>
+        <v>0.0005426623598601132</v>
       </c>
       <c r="F24" s="33" t="n">
-        <v>0.0005908186301670781</v>
+        <v>0.0005821700069987834</v>
       </c>
       <c r="G24" s="34" t="n">
-        <v>1.191369624117165</v>
+        <v>1.215187351922793</v>
       </c>
       <c r="H24" s="34" t="n">
-        <v>1.111702844573205</v>
+        <v>1.13272141838108</v>
       </c>
     </row>
     <row r="25" ht="15.95" customHeight="1">
@@ -1531,24 +1531,24 @@
     <row r="27" ht="15.95" customFormat="1" customHeight="1" s="26">
       <c r="B27" s="35" t="inlineStr">
         <is>
-          <t>Mar-26</t>
+          <t>Apr-26</t>
         </is>
       </c>
       <c r="C27" s="35" t="inlineStr"/>
       <c r="D27" s="29" t="n">
-        <v>0.01165881145243075</v>
+        <v>0.004492734197300674</v>
       </c>
       <c r="E27" s="29" t="n">
-        <v>0.00993531358511679</v>
+        <v>0.003804826246388782</v>
       </c>
       <c r="F27" s="29" t="n">
-        <v>0.01065336805133588</v>
+        <v>0.004082314319127534</v>
       </c>
       <c r="G27" s="30" t="n">
-        <v>1.173471914353643</v>
+        <v>1.180798781958781</v>
       </c>
       <c r="H27" s="30" t="n">
-        <v>1.094377984150167</v>
+        <v>1.100536079804079</v>
       </c>
       <c r="I27" s="36" t="n"/>
     </row>
@@ -1560,19 +1560,19 @@
       </c>
       <c r="C28" s="37" t="inlineStr"/>
       <c r="D28" s="33" t="n">
-        <v>0.01362897771737703</v>
+        <v>0.01363688963374687</v>
       </c>
       <c r="E28" s="33" t="n">
-        <v>0.01160659890087934</v>
+        <v>0.0115104208368324</v>
       </c>
       <c r="F28" s="33" t="n">
-        <v>0.01244576513139339</v>
+        <v>0.01234950728397388</v>
       </c>
       <c r="G28" s="34" t="n">
-        <v>1.174243879173293</v>
+        <v>1.18474292356974</v>
       </c>
       <c r="H28" s="34" t="n">
-        <v>1.095069493397323</v>
+        <v>1.10424564479942</v>
       </c>
       <c r="I28" s="38" t="n"/>
       <c r="J28" s="39" t="n"/>
@@ -1585,19 +1585,19 @@
       </c>
       <c r="C29" s="37" t="inlineStr"/>
       <c r="D29" s="33" t="n">
-        <v>0.04130565788049823</v>
+        <v>0.04144144875250499</v>
       </c>
       <c r="E29" s="33" t="n">
-        <v>0.03529708637135154</v>
+        <v>0.03519865594435645</v>
       </c>
       <c r="F29" s="33" t="n">
-        <v>0.0378756794085584</v>
+        <v>0.03777700382293214</v>
       </c>
       <c r="G29" s="34" t="n">
-        <v>1.170228540847028</v>
+        <v>1.177358840576681</v>
       </c>
       <c r="H29" s="34" t="n">
-        <v>1.090558863246814</v>
+        <v>1.097002000125494</v>
       </c>
       <c r="I29" s="38" t="n"/>
     </row>
@@ -1609,19 +1609,19 @@
       </c>
       <c r="C30" s="37" t="inlineStr"/>
       <c r="D30" s="33" t="n">
-        <v>0.08404363870450826</v>
+        <v>0.08407024252376472</v>
       </c>
       <c r="E30" s="33" t="n">
-        <v>0.07187711571831934</v>
+        <v>0.07177520746070365</v>
       </c>
       <c r="F30" s="33" t="n">
-        <v>0.07722316940950291</v>
+        <v>0.07712075287811992</v>
       </c>
       <c r="G30" s="34" t="n">
-        <v>1.169268380688348</v>
+        <v>1.17129919227043</v>
       </c>
       <c r="H30" s="34" t="n">
-        <v>1.088321540635524</v>
+        <v>1.090111797230865</v>
       </c>
       <c r="I30" s="38" t="n"/>
     </row>
@@ -1633,44 +1633,43 @@
       </c>
       <c r="C31" s="37" t="inlineStr"/>
       <c r="D31" s="33" t="n">
-        <v>0.1747662282221996</v>
+        <v>0.1749535495792958</v>
       </c>
       <c r="E31" s="33" t="n">
-        <v>0.1477970366518437</v>
+        <v>0.148016036262707</v>
       </c>
       <c r="F31" s="33" t="n">
-        <v>0.1592750070183817</v>
+        <v>0.1594961966253503</v>
       </c>
       <c r="G31" s="34" t="n">
-        <v>1.182474508158682</v>
+        <v>1.1819905058718</v>
       </c>
       <c r="H31" s="34" t="n">
-        <v>1.097260841445325</v>
+        <v>1.096913614750665</v>
       </c>
       <c r="I31" s="38" t="n"/>
     </row>
     <row r="32" ht="15.95" customFormat="1" customHeight="1" s="26">
-      <c r="A32" s="45" t="n"/>
       <c r="B32" s="37" t="inlineStr">
         <is>
-          <t>Ano 2026</t>
+          <t>Últimos 720 dias</t>
         </is>
       </c>
       <c r="C32" s="37" t="inlineStr"/>
       <c r="D32" s="33" t="n">
-        <v>0.03731803647725873</v>
+        <v>0.3421173431438711</v>
       </c>
       <c r="E32" s="33" t="n">
-        <v>0.03187906296972676</v>
+        <v>0.2779304689804314</v>
       </c>
       <c r="F32" s="33" t="n">
-        <v>0.03420409775832423</v>
+        <v>0.3036168714069436</v>
       </c>
       <c r="G32" s="34" t="n">
-        <v>1.170612715709272</v>
+        <v>1.230945798778035</v>
       </c>
       <c r="H32" s="34" t="n">
-        <v>1.091039931558395</v>
+        <v>1.126806101250298</v>
       </c>
       <c r="I32" s="38" t="n"/>
     </row>
@@ -1678,49 +1677,49 @@
       <c r="A33" s="45" t="n"/>
       <c r="B33" s="37" t="inlineStr">
         <is>
-          <t>Ano 2025</t>
+          <t>Ano 2026</t>
         </is>
       </c>
       <c r="C33" s="37" t="inlineStr"/>
       <c r="D33" s="33" t="n">
-        <v>0.1702997803064539</v>
+        <v>0.0447022135085775</v>
       </c>
       <c r="E33" s="33" t="n">
-        <v>0.143132751155109</v>
+        <v>0.0380553842733744</v>
       </c>
       <c r="F33" s="33" t="n">
-        <v>0.1545640786666771</v>
+        <v>0.04084631843637321</v>
       </c>
       <c r="G33" s="34" t="n">
-        <v>1.189803025038656</v>
+        <v>1.174661992307185</v>
       </c>
       <c r="H33" s="34" t="n">
-        <v>1.101806977245414</v>
+        <v>1.094400063942376</v>
       </c>
       <c r="I33" s="38" t="n"/>
     </row>
     <row r="34" ht="15.95" customFormat="1" customHeight="1" s="26">
-      <c r="A34" s="40" t="n"/>
+      <c r="A34" s="45" t="n"/>
       <c r="B34" s="37" t="inlineStr">
         <is>
-          <t>Ano 2024</t>
+          <t>Ano 2025</t>
         </is>
       </c>
       <c r="C34" s="37" t="inlineStr"/>
       <c r="D34" s="33" t="n">
-        <v>0.1393234465345621</v>
+        <v>0.1702997803064539</v>
       </c>
       <c r="E34" s="33" t="n">
-        <v>0.1092049264357533</v>
+        <v>0.143132751155109</v>
       </c>
       <c r="F34" s="33" t="n">
-        <v>0.1203854500312833</v>
+        <v>0.1545640786666771</v>
       </c>
       <c r="G34" s="34" t="n">
-        <v>1.275798181289265</v>
+        <v>1.189803025038656</v>
       </c>
       <c r="H34" s="34" t="n">
-        <v>1.157311340351824</v>
+        <v>1.101806977245414</v>
       </c>
       <c r="I34" s="38" t="n"/>
     </row>
@@ -1728,124 +1727,138 @@
       <c r="A35" s="40" t="n"/>
       <c r="B35" s="37" t="inlineStr">
         <is>
-          <t>Acumulado²</t>
+          <t>Ano 2024</t>
         </is>
       </c>
       <c r="C35" s="37" t="inlineStr"/>
       <c r="D35" s="33" t="n">
-        <v>0.5061499599999999</v>
+        <v>0.1393234465345621</v>
       </c>
       <c r="E35" s="33" t="n">
-        <v>0.4030222806963146</v>
+        <v>0.1092049264357533</v>
       </c>
       <c r="F35" s="33" t="n">
-        <v>0.4427981288980825</v>
+        <v>0.1203854500312833</v>
       </c>
       <c r="G35" s="34" t="n">
-        <v>1.255885801463652</v>
+        <v>1.275798181289265</v>
       </c>
       <c r="H35" s="34" t="n">
-        <v>1.143071587180304</v>
+        <v>1.157311340351824</v>
       </c>
       <c r="I35" s="38" t="n"/>
     </row>
-    <row r="36" ht="15.95" customHeight="1">
-      <c r="A36" s="3" t="n"/>
-      <c r="B36" s="10" t="n"/>
-      <c r="C36" s="7" t="n"/>
-      <c r="D36" s="7" t="n"/>
-      <c r="E36" s="7" t="n"/>
-      <c r="F36" s="7" t="n"/>
-      <c r="G36" s="7" t="n"/>
-      <c r="H36" s="7" t="n"/>
-      <c r="I36" s="3" t="n"/>
-    </row>
-    <row r="37" ht="26.1" customHeight="1">
-      <c r="B37" s="50" t="inlineStr">
+    <row r="36" ht="15.95" customFormat="1" customHeight="1" s="26">
+      <c r="A36" s="40" t="n"/>
+      <c r="B36" s="37" t="inlineStr">
+        <is>
+          <t>Acumulado²</t>
+        </is>
+      </c>
+      <c r="C36" s="37" t="inlineStr"/>
+      <c r="D36" s="33" t="n">
+        <v>0.51687153</v>
+      </c>
+      <c r="E36" s="33" t="n">
+        <v>0.41142008302871</v>
+      </c>
+      <c r="F36" s="33" t="n">
+        <v>0.4520645624645219</v>
+      </c>
+      <c r="G36" s="34" t="n">
+        <v>1.256310888362568</v>
+      </c>
+      <c r="H36" s="34" t="n">
+        <v>1.143357769921557</v>
+      </c>
+      <c r="I36" s="38" t="n"/>
+    </row>
+    <row r="37" ht="15.95" customHeight="1">
+      <c r="A37" s="3" t="n"/>
+      <c r="B37" s="10" t="n"/>
+      <c r="C37" s="7" t="n"/>
+      <c r="D37" s="7" t="n"/>
+      <c r="E37" s="7" t="n"/>
+      <c r="F37" s="7" t="n"/>
+      <c r="G37" s="7" t="n"/>
+      <c r="H37" s="7" t="n"/>
+      <c r="I37" s="3" t="n"/>
+    </row>
+    <row r="38" ht="26.1" customHeight="1">
+      <c r="B38" s="49" t="inlineStr">
         <is>
           <t>Patrimônio Líquido (R$)</t>
         </is>
       </c>
-      <c r="I37" s="3" t="n"/>
-    </row>
-    <row r="38" ht="15.95" customHeight="1">
-      <c r="B38" s="11" t="inlineStr">
+      <c r="I38" s="3" t="n"/>
+    </row>
+    <row r="39" ht="15.95" customHeight="1">
+      <c r="B39" s="11" t="inlineStr">
         <is>
           <t>Hoje¹</t>
-        </is>
-      </c>
-      <c r="C38" s="12" t="n"/>
-      <c r="D38" s="12" t="n"/>
-      <c r="E38" s="48" t="n">
-        <v>400795591.6</v>
-      </c>
-      <c r="I38" s="3" t="n"/>
-    </row>
-    <row r="39" ht="15.95" customHeight="1">
-      <c r="B39" s="13" t="inlineStr">
-        <is>
-          <t>Últimos 12 Meses (Média Diária)¹</t>
         </is>
       </c>
       <c r="C39" s="12" t="n"/>
       <c r="D39" s="12" t="n"/>
-      <c r="E39" s="48" t="n">
-        <v>295521488.3098413</v>
+      <c r="E39" s="46" t="n">
+        <v>413353044.32</v>
       </c>
       <c r="I39" s="3" t="n"/>
     </row>
     <row r="40" ht="15.95" customHeight="1">
-      <c r="B40" s="14" t="n"/>
-      <c r="C40" s="3" t="n"/>
-      <c r="D40" s="3" t="n"/>
-      <c r="E40" s="3" t="n"/>
-      <c r="F40" s="3" t="n"/>
-      <c r="G40" s="3" t="n"/>
-      <c r="H40" s="3" t="n"/>
+      <c r="B40" s="13" t="inlineStr">
+        <is>
+          <t>Últimos 12 Meses (Média Diária)¹</t>
+        </is>
+      </c>
+      <c r="C40" s="12" t="n"/>
+      <c r="D40" s="12" t="n"/>
+      <c r="E40" s="46" t="n">
+        <v>303314951.6346428</v>
+      </c>
       <c r="I40" s="3" t="n"/>
     </row>
     <row r="41" ht="15.95" customHeight="1">
-      <c r="A41" s="3" t="n"/>
-      <c r="B41" s="15" t="inlineStr">
-        <is>
-          <t>¹Data de Referência:</t>
-        </is>
-      </c>
-      <c r="C41" s="24" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="D41" s="17" t="n"/>
-      <c r="E41" s="17" t="n"/>
-      <c r="F41" s="17" t="n"/>
-      <c r="G41" s="17" t="n"/>
-      <c r="H41" s="17" t="n"/>
+      <c r="B41" s="14" t="n"/>
+      <c r="C41" s="3" t="n"/>
+      <c r="D41" s="3" t="n"/>
+      <c r="E41" s="3" t="n"/>
+      <c r="F41" s="3" t="n"/>
+      <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
       <c r="I41" s="3" t="n"/>
     </row>
     <row r="42" ht="15.95" customHeight="1">
       <c r="A42" s="3" t="n"/>
-      <c r="B42" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">²Cota Inicial em: </t>
+      <c r="B42" s="15" t="inlineStr">
+        <is>
+          <t>¹Data de Referência:</t>
         </is>
       </c>
       <c r="C42" s="24" t="inlineStr">
         <is>
-          <t>2023-06-01</t>
-        </is>
-      </c>
-      <c r="D42" s="19" t="n"/>
-      <c r="E42" s="19" t="n"/>
-      <c r="F42" s="19" t="n"/>
-      <c r="G42" s="19" t="n"/>
-      <c r="H42" s="19" t="n"/>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="D42" s="17" t="n"/>
+      <c r="E42" s="17" t="n"/>
+      <c r="F42" s="17" t="n"/>
+      <c r="G42" s="17" t="n"/>
+      <c r="H42" s="17" t="n"/>
       <c r="I42" s="3" t="n"/>
     </row>
     <row r="43" ht="15.95" customHeight="1">
       <c r="A43" s="3" t="n"/>
-      <c r="B43" s="18" t="n"/>
-      <c r="C43" s="16" t="n"/>
+      <c r="B43" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">²Cota Inicial em: </t>
+        </is>
+      </c>
+      <c r="C43" s="24" t="inlineStr">
+        <is>
+          <t>2023-06-01</t>
+        </is>
+      </c>
       <c r="D43" s="19" t="n"/>
       <c r="E43" s="19" t="n"/>
       <c r="F43" s="19" t="n"/>
@@ -1853,43 +1866,44 @@
       <c r="H43" s="19" t="n"/>
       <c r="I43" s="3" t="n"/>
     </row>
-    <row r="44" ht="43.5" customHeight="1">
+    <row r="44" ht="15.95" customHeight="1">
       <c r="A44" s="3" t="n"/>
-      <c r="B44" s="49" t="inlineStr">
+      <c r="B44" s="18" t="n"/>
+      <c r="C44" s="16" t="n"/>
+      <c r="D44" s="19" t="n"/>
+      <c r="E44" s="19" t="n"/>
+      <c r="F44" s="19" t="n"/>
+      <c r="G44" s="19" t="n"/>
+      <c r="H44" s="19" t="n"/>
+      <c r="I44" s="3" t="n"/>
+    </row>
+    <row r="45" ht="43.5" customHeight="1">
+      <c r="A45" s="3" t="n"/>
+      <c r="B45" s="48" t="inlineStr">
         <is>
           <t xml:space="preserve">As informações contidas neste material são de caráter exclusivamente informativo. Fundos de investimento não contam com garantia do administrador do fundo, do gestor da carteira, de qualquer mecanismo de seguro ou, ainda, do Fundo Garantidor de Créditos – FGC. Rentabilidade passada não representa garantia de rentabilidade futura. "A rentabilidade divulgada não é líquida de impostos.“ Leia o prospecto e o regulamento antes de investir. </t>
         </is>
       </c>
-      <c r="I44" s="3" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="n"/>
-      <c r="B45" s="46" t="n"/>
       <c r="I45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n"/>
-      <c r="B46" s="20" t="n"/>
-      <c r="C46" s="20" t="n"/>
-      <c r="D46" s="20" t="n"/>
-      <c r="E46" s="20" t="n"/>
-      <c r="F46" s="20" t="n"/>
-      <c r="G46" s="20" t="n"/>
-      <c r="H46" s="20" t="n"/>
+      <c r="B46" s="50" t="n"/>
       <c r="I46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n"/>
-      <c r="B47" s="21" t="n"/>
-      <c r="C47" s="22" t="n"/>
-      <c r="D47" s="9" t="n"/>
-      <c r="E47" s="9" t="n"/>
-      <c r="F47" s="9" t="n"/>
-      <c r="G47" s="9" t="n"/>
-      <c r="H47" s="9" t="n"/>
+      <c r="B47" s="20" t="n"/>
+      <c r="C47" s="20" t="n"/>
+      <c r="D47" s="20" t="n"/>
+      <c r="E47" s="20" t="n"/>
+      <c r="F47" s="20" t="n"/>
+      <c r="G47" s="20" t="n"/>
+      <c r="H47" s="20" t="n"/>
       <c r="I47" s="3" t="n"/>
     </row>
     <row r="48">
+      <c r="A48" s="3" t="n"/>
       <c r="B48" s="21" t="n"/>
       <c r="C48" s="22" t="n"/>
       <c r="D48" s="9" t="n"/>
@@ -1897,17 +1911,27 @@
       <c r="F48" s="9" t="n"/>
       <c r="G48" s="9" t="n"/>
       <c r="H48" s="9" t="n"/>
+      <c r="I48" s="3" t="n"/>
+    </row>
+    <row r="49">
+      <c r="B49" s="21" t="n"/>
+      <c r="C49" s="22" t="n"/>
+      <c r="D49" s="9" t="n"/>
+      <c r="E49" s="9" t="n"/>
+      <c r="F49" s="9" t="n"/>
+      <c r="G49" s="9" t="n"/>
+      <c r="H49" s="9" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="E40:H40"/>
     <mergeCell ref="E39:H39"/>
-    <mergeCell ref="B44:H44"/>
-    <mergeCell ref="E38:H38"/>
-    <mergeCell ref="B37:H37"/>
+    <mergeCell ref="B38:H38"/>
     <mergeCell ref="B45:H45"/>
+    <mergeCell ref="B46:H46"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="76" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="74"/>
 </worksheet>
 </file>